--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.70546</v>
+        <v>17.70874</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32649</v>
+        <v>16.93048</v>
       </c>
       <c r="E2" t="n">
-        <v>17.56452</v>
+        <v>17.52797</v>
       </c>
       <c r="F2" t="n">
-        <v>44.15187</v>
+        <v>44.42909</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05361</v>
+        <v>0.05213</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89757</v>
+        <v>1.92348</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.55402</v>
+        <v>17.90741</v>
       </c>
       <c r="D3" t="n">
-        <v>17.14064</v>
+        <v>17.58859</v>
       </c>
       <c r="E3" t="n">
-        <v>17.11978</v>
+        <v>17.74669</v>
       </c>
       <c r="F3" t="n">
-        <v>45.05347</v>
+        <v>43.89165</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05229</v>
+        <v>0.05321</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93454</v>
+        <v>1.9214</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.30003</v>
+        <v>17.51972</v>
       </c>
       <c r="D4" t="n">
-        <v>17.72956</v>
+        <v>17.18472</v>
       </c>
       <c r="E4" t="n">
-        <v>17.71274</v>
+        <v>17.27269</v>
       </c>
       <c r="F4" t="n">
-        <v>43.76282</v>
+        <v>45.25015</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05375</v>
+        <v>0.05272</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92946</v>
+        <v>1.89841</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.5978</v>
+        <v>17.59822</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86305</v>
+        <v>16.95192</v>
       </c>
       <c r="E6" t="n">
-        <v>17.22352</v>
+        <v>17.27229</v>
       </c>
       <c r="F6" t="n">
-        <v>22.41164</v>
+        <v>23.21342</v>
       </c>
       <c r="G6" t="n">
-        <v>35.66206</v>
+        <v>35.24571</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.55276</v>
+        <v>17.5418</v>
       </c>
       <c r="D7" t="n">
-        <v>16.823</v>
+        <v>16.76303</v>
       </c>
       <c r="E7" t="n">
-        <v>17.31576</v>
+        <v>17.28509</v>
       </c>
       <c r="F7" t="n">
-        <v>22.55808</v>
+        <v>23.17775</v>
       </c>
       <c r="G7" t="n">
-        <v>36.07346</v>
+        <v>35.5919</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.47777</v>
+        <v>17.38548</v>
       </c>
       <c r="D8" t="n">
-        <v>16.66039</v>
+        <v>16.58849</v>
       </c>
       <c r="E8" t="n">
-        <v>17.31271</v>
+        <v>17.25546</v>
       </c>
       <c r="F8" t="n">
-        <v>22.79757</v>
+        <v>22.86302</v>
       </c>
       <c r="G8" t="n">
-        <v>35.80327</v>
+        <v>35.8353</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.63696</v>
+        <v>0.62455</v>
       </c>
       <c r="D10" t="n">
-        <v>1.16937</v>
+        <v>1.20068</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.62497</v>
+        <v>0.6418199999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.16556</v>
+        <v>1.17325</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62688</v>
+        <v>0.6339</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17867</v>
+        <v>1.17097</v>
       </c>
     </row>
   </sheetData>
